--- a/data/trans_orig/P1431-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2012</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447456</t>
+          <t>447458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423228</t>
+          <t>423066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874580</t>
+          <t>874714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883340</t>
+          <t>883421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>676810</t>
+          <t>676973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686054</t>
+          <t>686066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>601173</t>
+          <t>600472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280634</t>
+          <t>1282259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1293500</t>
+          <t>1293409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677050</t>
+          <t>677107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697546</t>
+          <t>698617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707614</t>
+          <t>707648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379568</t>
+          <t>1379518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389421</t>
+          <t>1389368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602532</t>
+          <t>602816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612470</t>
+          <t>612501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600551</t>
+          <t>599685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611116</t>
+          <t>611132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207246</t>
+          <t>1207414</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1222420</t>
+          <t>1221493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19919</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>29700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413279</t>
+          <t>412806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425467</t>
+          <t>425346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427881</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442459</t>
+          <t>442583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>847076</t>
+          <t>847529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864518</t>
+          <t>864921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296275</t>
+          <t>295407</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306791</t>
+          <t>306810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333544</t>
+          <t>332296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348050</t>
+          <t>346989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>631868</t>
+          <t>633397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>650601</t>
+          <t>651030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>22082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34391</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226497</t>
+          <t>227769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>242670</t>
+          <t>243343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>369376</t>
+          <t>368715</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382411</t>
+          <t>382293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>603330</t>
+          <t>601849</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>622911</t>
+          <t>623591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55431</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68807</t>
+          <t>71483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,47 +3182,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>93968</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>76749</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>115093</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>93968</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>75815</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>116106</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3371348</t>
+          <t>3372003</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3397017</t>
+          <t>3397553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3485183</t>
+          <t>3482507</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3514796</t>
+          <t>3514694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,47 +3295,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6886801</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6865676</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6904020</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6886801</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6864663</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6904954</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2016</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,82 +3710,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>946</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391048</t>
+          <t>390621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810473</t>
+          <t>810517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>580365</t>
+          <t>581105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589554</t>
+          <t>589549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143550</t>
+          <t>1143731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153093</t>
+          <t>1153090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654198</t>
+          <t>655201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666148</t>
+          <t>666179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654678</t>
+          <t>654349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313471</t>
+          <t>1314722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325721</t>
+          <t>1326400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628728</t>
+          <t>629324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641716</t>
+          <t>641846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634026</t>
+          <t>634207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645894</t>
+          <t>646007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267098</t>
+          <t>1269093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1284762</t>
+          <t>1285505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>36445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458011</t>
+          <t>458721</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472392</t>
+          <t>472439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474951</t>
+          <t>473412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489367</t>
+          <t>489116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>936419</t>
+          <t>938322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959035</t>
+          <t>959114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317903</t>
+          <t>317396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>330391</t>
+          <t>329611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355626</t>
+          <t>356452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370722</t>
+          <t>370670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>680266</t>
+          <t>680003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>697978</t>
+          <t>697331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30469</t>
+          <t>32437</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245289</t>
+          <t>245299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254448</t>
+          <t>254444</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>369700</t>
+          <t>367732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>388821</t>
+          <t>387706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618767</t>
+          <t>618511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640783</t>
+          <t>640538</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75180</t>
+          <t>74301</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>83709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123618</t>
+          <t>123584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3335122</t>
+          <t>3334661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3360416</t>
+          <t>3361652</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3469362</t>
+          <t>3470241</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3501387</t>
+          <t>3502063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6815274</t>
+          <t>6815308</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6857345</t>
+          <t>6855183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1431-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Edad-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447458</t>
+          <t>447123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423066</t>
+          <t>423385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874714</t>
+          <t>874786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883421</t>
+          <t>883432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>676973</t>
+          <t>676741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686066</t>
+          <t>685877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600472</t>
+          <t>600517</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609254</t>
+          <t>609251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1282259</t>
+          <t>1281386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1293409</t>
+          <t>1293390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677107</t>
+          <t>677094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698617</t>
+          <t>698567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707648</t>
+          <t>707638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379518</t>
+          <t>1379542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389368</t>
+          <t>1389432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602816</t>
+          <t>602619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612501</t>
+          <t>612494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599685</t>
+          <t>599616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611132</t>
+          <t>611142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207414</t>
+          <t>1206962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221493</t>
+          <t>1222416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12308</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412806</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425346</t>
+          <t>425391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427318</t>
+          <t>427526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442583</t>
+          <t>442609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>847529</t>
+          <t>847659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864921</t>
+          <t>864969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295407</t>
+          <t>295779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306810</t>
+          <t>306798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332296</t>
+          <t>332333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346989</t>
+          <t>346850</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633397</t>
+          <t>633319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651030</t>
+          <t>651287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>15990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227769</t>
+          <t>227420</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243343</t>
+          <t>243445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368715</t>
+          <t>368760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382293</t>
+          <t>382465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601849</t>
+          <t>600755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623591</t>
+          <t>621731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>39653</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71483</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76749</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115093</t>
+          <t>115973</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3372003</t>
+          <t>3371561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3397553</t>
+          <t>3397679</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3482507</t>
+          <t>3485449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3514694</t>
+          <t>3514337</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6865676</t>
+          <t>6864796</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6904020</t>
+          <t>6904093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390621</t>
+          <t>391010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810517</t>
+          <t>810467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581105</t>
+          <t>580281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589549</t>
+          <t>589548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143731</t>
+          <t>1144874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153090</t>
+          <t>1153095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655201</t>
+          <t>655177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654349</t>
+          <t>654800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314722</t>
+          <t>1314370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326400</t>
+          <t>1326404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629324</t>
+          <t>628825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641846</t>
+          <t>641709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634207</t>
+          <t>634255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646007</t>
+          <t>645846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1269093</t>
+          <t>1268298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285505</t>
+          <t>1285871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36445</t>
+          <t>34969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458721</t>
+          <t>458121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472439</t>
+          <t>472501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473412</t>
+          <t>474677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489116</t>
+          <t>490051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938322</t>
+          <t>939798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959114</t>
+          <t>959975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317396</t>
+          <t>318353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329611</t>
+          <t>329505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>356452</t>
+          <t>356548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370670</t>
+          <t>370728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>680003</t>
+          <t>680409</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>697331</t>
+          <t>698059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32437</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245299</t>
+          <t>245172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254444</t>
+          <t>254493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367732</t>
+          <t>368699</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387706</t>
+          <t>388885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618511</t>
+          <t>618211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640538</t>
+          <t>639148</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>61551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74301</t>
+          <t>75001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,42 +6161,42 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>102298</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>83455</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>123761</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>102298</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>83709</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>123584</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3334661</t>
+          <t>3332799</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3361652</t>
+          <t>3360685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3470241</t>
+          <t>3469541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3502063</t>
+          <t>3501340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,47 +6274,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6473</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6836594</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6815131</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6855437</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>98,8%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6473</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6836594</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6815308</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6855183</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
         </is>
       </c>
     </row>
